--- a/output/pdf_financials_xlsx/RX.xlsx
+++ b/output/pdf_financials_xlsx/RX.xlsx
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.699251</v>
+        <v>5.346586</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>5.216537</v>
+        <v>7.884392</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>7.025987</v>
+        <v>10.222192</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>8.309158</v>
+        <v>12.052415</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>9.515167999999999</v>
+        <v>13.912591</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>9.672147000000001</v>
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2.475877</v>
+        <v>0.828542</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4.314341</v>
+        <v>1.646486</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.083767</v>
+        <v>1.887562</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5.817279</v>
+        <v>2.074022</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>6.459502</v>
+        <v>2.062079</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>6.79456</v>
@@ -2237,10 +2237,10 @@
         <v>0.04361</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1.957405</v>
+        <v>0.016228</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>2.289079</v>
+        <v>0.052384</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
@@ -2283,10 +2283,10 @@
         <v>1.385278</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>3.898582</v>
+        <v>1.957405</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>4.919634</v>
+        <v>2.682939</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>2.692222</v>
@@ -2605,7 +2605,7 @@
         <v>0.33236</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0</v>
+        <v>0.285501</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>OtherReceivables</t>
+          <t>AccountsReceivable</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -43172,7 +43172,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -43330,7 +43330,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -46735,7 +46735,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -46897,7 +46897,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -52608,7 +52608,7 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -53554,7 +53554,7 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
@@ -54632,7 +54632,7 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E613" s="5" t="n">

--- a/output/pdf_financials_xlsx/RX.xlsx
+++ b/output/pdf_financials_xlsx/RX.xlsx
@@ -1721,37 +1721,37 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.005966</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.065716</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.09798999999999999</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.185286</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.29173</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.510422</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.457106</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.450998</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.455338</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.589948</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.852491</v>
       </c>
     </row>
     <row r="29">
@@ -1767,37 +1767,37 @@
         <v>4.399088</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5.274619</v>
+        <v>5.280585</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.986272</v>
+        <v>6.051988</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7.320703</v>
+        <v>7.418693</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>8.299052</v>
+        <v>8.484337999999999</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>6.385377</v>
+        <v>6.677107</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>5.536876</v>
+        <v>6.047298</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>8.533887</v>
+        <v>8.990993</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>7.956446</v>
+        <v>8.407444</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>9.664977</v>
+        <v>10.120315</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>10.871084</v>
+        <v>11.461032</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>12.916466</v>
+        <v>13.768957</v>
       </c>
     </row>
     <row r="30">
@@ -1813,37 +1813,37 @@
         <v>36.02524156861197</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>34.27704586034646</v>
+        <v>34.31581583702209</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>33.40130463384381</v>
+        <v>33.76797693595734</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>35.2588228296293</v>
+        <v>35.73077368586202</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>38.55177779301444</v>
+        <v>39.41249112511026</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>29.80433361631387</v>
+        <v>31.16601018543222</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>24.79327578047953</v>
+        <v>27.07886668235704</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>29.8197707488286</v>
+        <v>31.41702603565323</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>28.49200615917093</v>
+        <v>30.10702846860077</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>30.59475974620312</v>
+        <v>32.03614514353171</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>31.03284509100638</v>
+        <v>32.71692414841675</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>30.00202336788993</v>
+        <v>31.98216676802088</v>
       </c>
     </row>
     <row r="31">
@@ -5007,37 +5007,37 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.005966</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.065716</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.09798999999999999</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.185286</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.29173</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.510422</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.457106</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.450998</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.455338</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.589948</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.852491</v>
       </c>
     </row>
     <row r="101">
@@ -21383,7 +21383,11 @@
           <t>Depreciation - property and equipment (Notes 13, 18)</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -21460,7 +21464,11 @@
           <t>Amortization - intangible assets (Notes 14, 18)</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -22758,7 +22766,11 @@
           <t>Net additions to intangible assets (Note 14)</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -26464,7 +26476,11 @@
           <t>Depreciation - property and equipment (Notes 12, 17)</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -26543,7 +26559,11 @@
           <t>Amortization - intangible assets (Notes 13, 17)</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -27337,7 +27357,11 @@
           <t>Net additions to intangible assets (Note 13)</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -29316,7 +29340,11 @@
           <t>Depreciation - property and equipment (Notes 11, 17)</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -29395,7 +29423,11 @@
           <t>Amortization - intangible assets (Notes 12, 17)</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -29946,7 +29978,11 @@
           <t>Net additions to intangible assets (Note 12)</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -31419,7 +31455,11 @@
           <t>Depreciation - property and equipment (Notes 11, 18)</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -31498,7 +31538,11 @@
           <t>Amortization - intangible assets (Notes 12, 18)</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -31897,7 +31941,11 @@
           <t>Additions to intangible assets (Note 12)</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -33627,7 +33675,11 @@
           <t>Depreciation - property and equipment (Note 10)</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -33706,7 +33758,11 @@
           <t>Amortization - intangible assets (Note 11)</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -34403,7 +34459,11 @@
           <t>Additions to intangible assets (Note 11)</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -38298,7 +38358,11 @@
           <t>Amortization – intangible assets (Note 11)</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -39570,7 +39634,11 @@
           <t>Amortization - intangible assets</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -39961,7 +40029,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -41166,7 +41238,11 @@
           <t>Additions to Intangible Assets</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E443" s="5" t="n">
         <v>-0.052994</v>
       </c>

--- a/output/pdf_financials_xlsx/RX.xlsx
+++ b/output/pdf_financials_xlsx/RX.xlsx
@@ -1739,7 +1739,7 @@
         <v>0.510422</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.457106</v>
+        <v>0.000752</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0.450998</v>
@@ -1785,7 +1785,7 @@
         <v>6.047298</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>8.990993</v>
+        <v>8.534639</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>8.407444</v>
@@ -1831,7 +1831,7 @@
         <v>27.07886668235704</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>31.41702603565323</v>
+        <v>29.82239844563347</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>30.10702846860077</v>
@@ -2243,28 +2243,28 @@
         <v>0.052384</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.076142</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.268809</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.215987</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.292928</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.317758</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.025329</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.034191</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.063442</v>
       </c>
     </row>
     <row r="41">
@@ -2289,28 +2289,28 @@
         <v>2.682939</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>2.692222</v>
+        <v>2.768364</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>2.67219</v>
+        <v>2.940999</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.412347</v>
+        <v>2.628334</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>2.787305</v>
+        <v>3.080233</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>3.498355</v>
+        <v>3.816113</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>3.477096</v>
+        <v>3.502425</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>2.906829</v>
+        <v>2.94102</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>4.456562</v>
+        <v>4.520004</v>
       </c>
     </row>
     <row r="42">
@@ -2614,25 +2614,25 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.060314</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.876138</v>
+        <v>0.58321</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.413487</v>
+        <v>0.09572899999999999</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.312879</v>
+        <v>0.28755</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.295194</v>
+        <v>0.261003</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.268372</v>
+        <v>0.20493</v>
       </c>
     </row>
     <row r="49">
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.07796500000000001</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.061463</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -5982,28 +5982,28 @@
         <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-0.606193</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-6.351603</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-2.648194</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-1.321594</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-3.368691</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-3.068899</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-5.17666</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-0.215</v>
       </c>
     </row>
     <row r="122">
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.07796500000000001</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.061463</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -6637,10 +6637,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>2.152242</v>
+        <v>2.074277</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>3.640013</v>
+        <v>3.57855</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>2.81092</v>
@@ -21853,7 +21853,11 @@
           <t>Deferred tax recovery (Note 25)</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -23378,7 +23382,11 @@
           <t>Repurchase of common shares - NCIB (Note 17)</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -26960,7 +26968,11 @@
           <t>Deferred tax recovery (Note 24)</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -27912,7 +27924,11 @@
           <t>Repurchase of common shares - NCIB (Note 16)</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -34939,7 +34955,11 @@
           <t>Repurchase of common shares - NCIB (Note 14)</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
@@ -36766,7 +36786,11 @@
           <t>Repurchase of common shares – NCIB</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -41159,7 +41183,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E442" s="5" t="n">
         <v>-0.07796500000000001</v>
       </c>
@@ -49849,7 +49877,11 @@
           <t>certain trademarks and technology related thereto. The product has   $3,936 (December 31, 2021 - $3,936). This asset is being asset has not yet commenced. December 31, 2022, $781 of amortization expense ( 2021</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
           <t>-</t>
